--- a/Desarrollo/Sistema de Control de Peso (SISCOP)/Analisis/SISCOP-C.xlsx
+++ b/Desarrollo/Sistema de Control de Peso (SISCOP)/Analisis/SISCOP-C.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Copia de Hoja1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Actual" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="tWP+FX2LbnqvpL6Y9F0zyrBf0pSRN7wKP35kEJKmNaY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lImt7skTHQI0K37atrQxxgvxH+gFsuaTlqoSHCPpcFs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="177">
   <si>
     <t>CRONOGRAMA DEL PROYECTO</t>
   </si>
@@ -312,6 +312,9 @@
     <t>SISCOP-PF.fig</t>
   </si>
   <si>
+    <t>Medrano/UX/UI, Ccahuana/Frontend</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -328,15 +331,6 @@
   </si>
   <si>
     <t>Revisar y validar diseño del sistema</t>
-  </si>
-  <si>
-    <t>Diseñar prototipo navegable</t>
-  </si>
-  <si>
-    <t>Prototipo navegable en Figma</t>
-  </si>
-  <si>
-    <t>SISCOP-PN.fig</t>
   </si>
   <si>
     <t>Diseñar pruebas de software</t>
@@ -357,9 +351,6 @@
     <t>Ccahuana/Frontend, Rosales/Analista QA, Gil/Dev Backend, Medrano/UX/UI</t>
   </si>
   <si>
-    <t>Configurar repositorio y ramas de trabajo</t>
-  </si>
-  <si>
     <t>Desarrollo del backend</t>
   </si>
   <si>
@@ -369,10 +360,10 @@
     <t>Módulo de conexión a BD</t>
   </si>
   <si>
-    <t>SISCOP-CBD.py</t>
+    <t>SISCOP-CBD.js</t>
   </si>
   <si>
-    <t>Gil/Dev Backend, Nuñez/DBA</t>
+    <t>Gil/Dev Backend, Nuñez/DBA, Carrascal/Tester/Analista de requisitos</t>
   </si>
   <si>
     <t>Implementar entidades y modelos del sistema</t>
@@ -381,7 +372,7 @@
     <t>Modelos del sistema</t>
   </si>
   <si>
-    <t>SISCOP-MOD.py</t>
+    <t>SISCOP-MOD.js</t>
   </si>
   <si>
     <t>Implementar lógica de negocio</t>
@@ -390,7 +381,7 @@
     <t>Servicios del sistema</t>
   </si>
   <si>
-    <t>SISCOP-SRV.py</t>
+    <t>SISCOP-SRV.js</t>
   </si>
   <si>
     <t>Implementar endpoints de la API</t>
@@ -399,7 +390,7 @@
     <t>API REST funcional</t>
   </si>
   <si>
-    <t>SISCOP-API.py</t>
+    <t>SISCOP-API.js</t>
   </si>
   <si>
     <t>Implementar módulo de autenticación</t>
@@ -408,7 +399,7 @@
     <t>Módulo de autenticación</t>
   </si>
   <si>
-    <t>SISCOP-AUTH.py</t>
+    <t>SISCOP-AUTH.js</t>
   </si>
   <si>
     <t>Implementar validaciones backend</t>
@@ -417,7 +408,7 @@
     <t>Validaciones backend</t>
   </si>
   <si>
-    <t>SISCOP-VBACK.py</t>
+    <t>SISCOP-VBACK.js</t>
   </si>
   <si>
     <t>Implementar generación de reportes PDF</t>
@@ -426,7 +417,7 @@
     <t>Módulo de reportes</t>
   </si>
   <si>
-    <t>SISCOP-RPDF.py</t>
+    <t>SISCOP-RPDF.js</t>
   </si>
   <si>
     <t>Desarrollo del frontend</t>
@@ -438,10 +429,10 @@
     <t>Sistema de rutas</t>
   </si>
   <si>
-    <t>SISCOP-ROUTES.jsx</t>
+    <t>SISCOP-ROUTES.tsx</t>
   </si>
   <si>
-    <t>Ccahuana/Frontend, Medrano/UX/UI</t>
+    <t>Ccahuana/Frontend, Medrano/UX/UI, Rosales/Analista QA</t>
   </si>
   <si>
     <t>Implementar interfaz de autenticación</t>
@@ -450,7 +441,7 @@
     <t>Pantalla de autenticación</t>
   </si>
   <si>
-    <t>SISCOP-LOGIN.jsx</t>
+    <t>SISCOP-LOGIN.tsx</t>
   </si>
   <si>
     <t>Implementar interfaz de gestión de pacientes</t>
@@ -459,7 +450,7 @@
     <t>Interfaces funcionales de pacientes</t>
   </si>
   <si>
-    <t>SISCOP-PAC.jsx</t>
+    <t>SISCOP-PAC.tsx</t>
   </si>
   <si>
     <t>Implementar interfaz de historia clínica</t>
@@ -468,7 +459,7 @@
     <t>Interfaces funcionales de historia clínica</t>
   </si>
   <si>
-    <t>SISCOP-HC.jsx</t>
+    <t>SISCOP-HC.tsx</t>
   </si>
   <si>
     <t>Implementar interfaz de evaluación nutricional</t>
@@ -477,7 +468,7 @@
     <t>Interfaces funcionales de evaluación</t>
   </si>
   <si>
-    <t>SISCOP-EVN.jsx</t>
+    <t>SISCOP-EVN.tsx</t>
   </si>
   <si>
     <t>Implementar visualización gráfica de evolución</t>
@@ -486,7 +477,7 @@
     <t>Módulo gráfico</t>
   </si>
   <si>
-    <t>SISCOP-GRAF.jsx</t>
+    <t>SISCOP-GRAF.tsx</t>
   </si>
   <si>
     <t>Corregir conflictos y commits pendientes</t>
@@ -2096,7 +2087,7 @@
         <v>46146.0</v>
       </c>
       <c r="H27" s="25">
-        <v>0.3</v>
+        <v>1.0</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -2245,10 +2236,10 @@
         <v>46147.0</v>
       </c>
       <c r="G31" s="18">
-        <v>46153.0</v>
+        <v>46158.0</v>
       </c>
       <c r="H31" s="25">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -2287,10 +2278,10 @@
         <v>46149.0</v>
       </c>
       <c r="G32" s="18">
-        <v>46152.0</v>
+        <v>46158.0</v>
       </c>
       <c r="H32" s="25">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -2323,21 +2314,21 @@
         <v>97</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="F33" s="18">
         <v>46149.0</v>
       </c>
       <c r="G33" s="18">
-        <v>46153.0</v>
+        <v>46158.0</v>
       </c>
       <c r="H33" s="25">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -2358,16 +2349,16 @@
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F34" s="18">
         <v>46153.0</v>
@@ -2376,7 +2367,7 @@
         <v>46157.0</v>
       </c>
       <c r="H34" s="25">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -2400,7 +2391,7 @@
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
@@ -2411,10 +2402,10 @@
         <v>46153.0</v>
       </c>
       <c r="G35" s="22">
-        <v>46156.0</v>
+        <v>46159.0</v>
       </c>
       <c r="H35" s="23">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -2438,25 +2429,25 @@
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F36" s="18">
-        <v>46153.0</v>
+        <v>46152.0</v>
       </c>
       <c r="G36" s="18">
-        <v>46159.0</v>
+        <v>46157.0</v>
       </c>
       <c r="H36" s="25">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -2479,26 +2470,22 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="18">
-        <v>46152.0</v>
-      </c>
-      <c r="G37" s="18">
-        <v>46157.0</v>
-      </c>
-      <c r="H37" s="25">
-        <v>0.0</v>
+      <c r="B37" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="22">
+        <v>46159.0</v>
+      </c>
+      <c r="G37" s="22">
+        <v>46159.0</v>
+      </c>
+      <c r="H37" s="23">
+        <v>1.0</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -2522,7 +2509,7 @@
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C38" s="33"/>
       <c r="D38" s="33"/>
@@ -2530,13 +2517,13 @@
         <v>83</v>
       </c>
       <c r="F38" s="22">
-        <v>46159.0</v>
+        <v>46160.0</v>
       </c>
       <c r="G38" s="22">
-        <v>46159.0</v>
+        <v>46160.0</v>
       </c>
       <c r="H38" s="23">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -2558,24 +2545,20 @@
       <c r="Z38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F39" s="22">
+      <c r="A39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="28">
         <v>46160.0</v>
       </c>
-      <c r="G39" s="22">
-        <v>46160.0</v>
-      </c>
-      <c r="H39" s="23">
-        <v>0.0</v>
-      </c>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="9"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -2596,20 +2579,24 @@
       <c r="Z39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="34" t="s">
+      <c r="A40" s="1"/>
+      <c r="B40" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" s="33"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C40" s="28">
+      <c r="F40" s="22">
         <v>46160.0</v>
       </c>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="9"/>
+      <c r="G40" s="22">
+        <v>46161.0</v>
+      </c>
+      <c r="H40" s="23">
+        <v>0.0</v>
+      </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -2631,23 +2618,15 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F41" s="22">
-        <v>46160.0</v>
-      </c>
-      <c r="G41" s="22">
-        <v>46161.0</v>
-      </c>
-      <c r="H41" s="23">
-        <v>0.0</v>
-      </c>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="9"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -2669,21 +2648,25 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" s="22">
-        <v>46160.0</v>
-      </c>
-      <c r="G42" s="22">
-        <v>46161.0</v>
-      </c>
-      <c r="H42" s="23">
+      <c r="D42" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" s="38">
+        <v>46162.0</v>
+      </c>
+      <c r="G42" s="38">
+        <v>46163.0</v>
+      </c>
+      <c r="H42" s="25">
         <v>0.0</v>
       </c>
       <c r="I42" s="3"/>
@@ -2707,15 +2690,27 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="9"/>
+      <c r="B43" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" s="38">
+        <v>46162.0</v>
+      </c>
+      <c r="G43" s="38">
+        <v>46165.0</v>
+      </c>
+      <c r="H43" s="25">
+        <v>0.0</v>
+      </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
@@ -2738,22 +2733,22 @@
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="E44" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C44" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>118</v>
-      </c>
       <c r="F44" s="38">
-        <v>46162.0</v>
+        <v>46164.0</v>
       </c>
       <c r="G44" s="38">
-        <v>46163.0</v>
+        <v>46170.0</v>
       </c>
       <c r="H44" s="25">
         <v>0.0</v>
@@ -2780,22 +2775,22 @@
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F45" s="38">
-        <v>46162.0</v>
+        <v>46166.0</v>
       </c>
       <c r="G45" s="38">
-        <v>46165.0</v>
+        <v>46171.0</v>
       </c>
       <c r="H45" s="25">
         <v>0.0</v>
@@ -2822,22 +2817,22 @@
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F46" s="38">
         <v>46164.0</v>
       </c>
       <c r="G46" s="38">
-        <v>46170.0</v>
+        <v>46167.0</v>
       </c>
       <c r="H46" s="25">
         <v>0.0</v>
@@ -2864,22 +2859,22 @@
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D47" s="37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F47" s="38">
-        <v>46166.0</v>
+        <v>46168.0</v>
       </c>
       <c r="G47" s="38">
-        <v>46171.0</v>
+        <v>46172.0</v>
       </c>
       <c r="H47" s="25">
         <v>0.0</v>
@@ -2906,22 +2901,22 @@
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F48" s="38">
-        <v>46164.0</v>
+        <v>46172.0</v>
       </c>
       <c r="G48" s="38">
-        <v>46167.0</v>
+        <v>46175.0</v>
       </c>
       <c r="H48" s="25">
         <v>0.0</v>
@@ -2947,27 +2942,15 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F49" s="38">
-        <v>46168.0</v>
-      </c>
-      <c r="G49" s="38">
-        <v>46172.0</v>
-      </c>
-      <c r="H49" s="25">
-        <v>0.0</v>
-      </c>
+      <c r="B49" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="9"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -2990,22 +2973,22 @@
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="D50" s="37" t="s">
         <v>136</v>
       </c>
+      <c r="D50" s="39" t="s">
+        <v>137</v>
+      </c>
       <c r="E50" s="17" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="F50" s="38">
-        <v>46172.0</v>
+        <v>46162.0</v>
       </c>
       <c r="G50" s="38">
-        <v>46175.0</v>
+        <v>46164.0</v>
       </c>
       <c r="H50" s="25">
         <v>0.0</v>
@@ -3031,15 +3014,27 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="9"/>
+      <c r="B51" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F51" s="38">
+        <v>46164.0</v>
+      </c>
+      <c r="G51" s="38">
+        <v>46166.0</v>
+      </c>
+      <c r="H51" s="25">
+        <v>0.0</v>
+      </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
@@ -3062,22 +3057,22 @@
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C52" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="D52" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>141</v>
-      </c>
       <c r="F52" s="38">
-        <v>46162.0</v>
+        <v>46165.0</v>
       </c>
       <c r="G52" s="38">
-        <v>46164.0</v>
+        <v>46169.0</v>
       </c>
       <c r="H52" s="25">
         <v>0.0</v>
@@ -3104,22 +3099,22 @@
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="17" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F53" s="38">
-        <v>46164.0</v>
+        <v>46167.0</v>
       </c>
       <c r="G53" s="38">
-        <v>46166.0</v>
+        <v>46171.0</v>
       </c>
       <c r="H53" s="25">
         <v>0.0</v>
@@ -3146,22 +3141,22 @@
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F54" s="38">
-        <v>46165.0</v>
+        <v>46169.0</v>
       </c>
       <c r="G54" s="38">
-        <v>46169.0</v>
+        <v>46173.0</v>
       </c>
       <c r="H54" s="25">
         <v>0.0</v>
@@ -3188,22 +3183,22 @@
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F55" s="38">
-        <v>46167.0</v>
+        <v>46172.0</v>
       </c>
       <c r="G55" s="38">
-        <v>46171.0</v>
+        <v>46175.0</v>
       </c>
       <c r="H55" s="25">
         <v>0.0</v>
@@ -3229,25 +3224,21 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F56" s="38">
-        <v>46169.0</v>
-      </c>
-      <c r="G56" s="38">
-        <v>46173.0</v>
-      </c>
-      <c r="H56" s="25">
+      <c r="B56" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="33"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" s="22">
+        <v>46176.0</v>
+      </c>
+      <c r="G56" s="22">
+        <v>46176.0</v>
+      </c>
+      <c r="H56" s="23">
         <v>0.0</v>
       </c>
       <c r="I56" s="3"/>
@@ -3271,25 +3262,21 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C57" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F57" s="38">
-        <v>46172.0</v>
-      </c>
-      <c r="G57" s="38">
-        <v>46175.0</v>
-      </c>
-      <c r="H57" s="25">
+      <c r="C57" s="33"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" s="22">
+        <v>46177.0</v>
+      </c>
+      <c r="G57" s="22">
+        <v>46177.0</v>
+      </c>
+      <c r="H57" s="23">
         <v>0.0</v>
       </c>
       <c r="I57" s="3"/>
@@ -3313,23 +3300,17 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F58" s="22">
-        <v>46176.0</v>
-      </c>
-      <c r="G58" s="22">
-        <v>46176.0</v>
-      </c>
-      <c r="H58" s="23">
-        <v>0.0</v>
-      </c>
+      <c r="B58" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="28">
+        <v>46178.0</v>
+      </c>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="9"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -3351,21 +3332,25 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C59" s="33"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F59" s="22">
-        <v>46177.0</v>
-      </c>
-      <c r="G59" s="22">
-        <v>46177.0</v>
-      </c>
-      <c r="H59" s="23">
+      <c r="D59" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" s="18">
+        <v>46178.0</v>
+      </c>
+      <c r="G59" s="18">
+        <v>46180.0</v>
+      </c>
+      <c r="H59" s="25">
         <v>0.0</v>
       </c>
       <c r="I59" s="3"/>
@@ -3389,17 +3374,27 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="C60" s="28">
-        <v>46178.0</v>
-      </c>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="9"/>
+      <c r="B60" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F60" s="18">
+        <v>46183.0</v>
+      </c>
+      <c r="G60" s="18">
+        <v>46185.0</v>
+      </c>
+      <c r="H60" s="25">
+        <v>0.0</v>
+      </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -3421,25 +3416,25 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>160</v>
+      <c r="B61" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>165</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="E61" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F61" s="18">
-        <v>46178.0</v>
-      </c>
-      <c r="G61" s="18">
-        <v>46180.0</v>
-      </c>
-      <c r="H61" s="25">
+        <v>166</v>
+      </c>
+      <c r="E61" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F61" s="38">
+        <v>46185.0</v>
+      </c>
+      <c r="G61" s="38">
+        <v>46187.0</v>
+      </c>
+      <c r="H61" s="41">
         <v>0.0</v>
       </c>
       <c r="I61" s="3"/>
@@ -3463,27 +3458,17 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F62" s="18">
-        <v>46183.0</v>
-      </c>
-      <c r="G62" s="18">
-        <v>46185.0</v>
-      </c>
-      <c r="H62" s="25">
-        <v>0.0</v>
-      </c>
+      <c r="B62" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="28">
+        <v>46188.0</v>
+      </c>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="9"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -3505,25 +3490,25 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="D63" s="31" t="s">
+      <c r="B63" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="C63" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="F63" s="38">
-        <v>46185.0</v>
-      </c>
-      <c r="G63" s="38">
-        <v>46187.0</v>
-      </c>
-      <c r="H63" s="41">
+      <c r="D63" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="18">
+        <v>46188.0</v>
+      </c>
+      <c r="G63" s="18">
+        <v>46189.0</v>
+      </c>
+      <c r="H63" s="25">
         <v>0.0</v>
       </c>
       <c r="I63" s="3"/>
@@ -3547,17 +3532,27 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
-      <c r="B64" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="C64" s="28">
+      <c r="B64" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F64" s="18">
         <v>46188.0</v>
       </c>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="9"/>
+      <c r="G64" s="18">
+        <v>46189.0</v>
+      </c>
+      <c r="H64" s="25">
+        <v>0.0</v>
+      </c>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
@@ -3579,25 +3574,21 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="D65" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="E65" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F65" s="18">
-        <v>46188.0</v>
-      </c>
-      <c r="G65" s="18">
-        <v>46189.0</v>
-      </c>
-      <c r="H65" s="25">
+      <c r="B65" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C65" s="21"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F65" s="22">
+        <v>46190.0</v>
+      </c>
+      <c r="G65" s="22">
+        <v>46190.0</v>
+      </c>
+      <c r="H65" s="23">
         <v>0.0</v>
       </c>
       <c r="I65" s="3"/>
@@ -3621,27 +3612,17 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C66" s="17" t="s">
+      <c r="B66" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="D66" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="F66" s="18">
-        <v>46188.0</v>
-      </c>
-      <c r="G66" s="18">
-        <v>46189.0</v>
-      </c>
-      <c r="H66" s="25">
-        <v>0.0</v>
-      </c>
+      <c r="C66" s="28">
+        <v>46190.0</v>
+      </c>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="9"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
@@ -3663,23 +3644,13 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="F67" s="22">
-        <v>46190.0</v>
-      </c>
-      <c r="G67" s="22">
-        <v>46190.0</v>
-      </c>
-      <c r="H67" s="23">
-        <v>0.0</v>
-      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="1"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
@@ -3700,18 +3671,14 @@
       <c r="Z67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="C68" s="28">
-        <v>46190.0</v>
-      </c>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="9"/>
+      <c r="A68" s="45"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="1"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
@@ -3735,7 +3702,7 @@
       <c r="A69" s="1"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="44"/>
+      <c r="D69" s="46"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -3760,7 +3727,7 @@
       <c r="Z69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="45"/>
+      <c r="A70" s="1"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="46"/>
@@ -3844,7 +3811,9 @@
       <c r="Z72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="1"/>
+      <c r="A73" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="46"/>
@@ -3900,9 +3869,7 @@
       <c r="Z74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="A75" s="1"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="46"/>
@@ -30307,13 +30274,6 @@
     </row>
     <row r="1018" ht="15.75" customHeight="1">
       <c r="A1018" s="1"/>
-      <c r="B1018" s="3"/>
-      <c r="C1018" s="3"/>
-      <c r="D1018" s="46"/>
-      <c r="E1018" s="3"/>
-      <c r="F1018" s="3"/>
-      <c r="G1018" s="3"/>
-      <c r="H1018" s="1"/>
       <c r="I1018" s="3"/>
       <c r="J1018" s="3"/>
       <c r="K1018" s="3"/>
@@ -30335,13 +30295,6 @@
     </row>
     <row r="1019" ht="15.75" customHeight="1">
       <c r="A1019" s="1"/>
-      <c r="B1019" s="3"/>
-      <c r="C1019" s="3"/>
-      <c r="D1019" s="46"/>
-      <c r="E1019" s="3"/>
-      <c r="F1019" s="3"/>
-      <c r="G1019" s="3"/>
-      <c r="H1019" s="1"/>
       <c r="I1019" s="3"/>
       <c r="J1019" s="3"/>
       <c r="K1019" s="3"/>
@@ -30655,56 +30608,8 @@
       <c r="Y1033" s="3"/>
       <c r="Z1033" s="3"/>
     </row>
-    <row r="1034" ht="15.75" customHeight="1">
-      <c r="A1034" s="1"/>
-      <c r="I1034" s="3"/>
-      <c r="J1034" s="3"/>
-      <c r="K1034" s="3"/>
-      <c r="L1034" s="3"/>
-      <c r="M1034" s="3"/>
-      <c r="N1034" s="3"/>
-      <c r="O1034" s="3"/>
-      <c r="P1034" s="3"/>
-      <c r="Q1034" s="3"/>
-      <c r="R1034" s="3"/>
-      <c r="S1034" s="3"/>
-      <c r="T1034" s="3"/>
-      <c r="U1034" s="3"/>
-      <c r="V1034" s="3"/>
-      <c r="W1034" s="3"/>
-      <c r="X1034" s="3"/>
-      <c r="Y1034" s="3"/>
-      <c r="Z1034" s="3"/>
-    </row>
-    <row r="1035" ht="15.75" customHeight="1">
-      <c r="A1035" s="1"/>
-      <c r="I1035" s="3"/>
-      <c r="J1035" s="3"/>
-      <c r="K1035" s="3"/>
-      <c r="L1035" s="3"/>
-      <c r="M1035" s="3"/>
-      <c r="N1035" s="3"/>
-      <c r="O1035" s="3"/>
-      <c r="P1035" s="3"/>
-      <c r="Q1035" s="3"/>
-      <c r="R1035" s="3"/>
-      <c r="S1035" s="3"/>
-      <c r="T1035" s="3"/>
-      <c r="U1035" s="3"/>
-      <c r="V1035" s="3"/>
-      <c r="W1035" s="3"/>
-      <c r="X1035" s="3"/>
-      <c r="Y1035" s="3"/>
-      <c r="Z1035" s="3"/>
-    </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
@@ -30712,34 +30617,40 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="C64:H64"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="B43:H43"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C66:H66"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C68:H68"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E12:E29 E31:E39 E41:E42 E44:E50 E52:E59 E61:E63 E65:E67">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E12:E29 E31:E38 E40 E42:E48 E50:E57 E59:E61 E63:E65">
       <formula1>"Ccahuana/Frontend,Guevara/Jefe de proyecto,Medrano/UX/UI,Nuñez/DBA,Gil/Dev Backend,Carrascal/Tester/Analista de requisitos,Rosales/Analista QA,Todos"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" prompt="Introduce un número entre 0 y 1 " sqref="H12:H29 H31:H39 H41:H42 H44:H50 H52:H59 H61:H63 H65:H67">
+    <dataValidation type="decimal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" prompt="Introduce un número entre 0 y 1 " sqref="H12:H29 H31:H38 H40 H42:H48 H50:H57 H59:H61 H63:H65">
       <formula1>0.0</formula1>
       <formula2>1.0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C3"/>
-    <hyperlink r:id="rId2" ref="D44"/>
-    <hyperlink r:id="rId3" ref="D45"/>
-    <hyperlink r:id="rId4" ref="D46"/>
-    <hyperlink r:id="rId5" ref="D47"/>
-    <hyperlink r:id="rId6" ref="D48"/>
-    <hyperlink r:id="rId7" ref="D49"/>
-    <hyperlink r:id="rId8" ref="D50"/>
+    <hyperlink r:id="rId2" ref="D42"/>
+    <hyperlink r:id="rId3" ref="D43"/>
+    <hyperlink r:id="rId4" ref="D44"/>
+    <hyperlink r:id="rId5" ref="D45"/>
+    <hyperlink r:id="rId6" ref="D46"/>
+    <hyperlink r:id="rId7" ref="D47"/>
+    <hyperlink r:id="rId8" ref="D48"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
